--- a/ksoft_old/docs/records/Internacional_Expenses_Records.xlsx
+++ b/ksoft_old/docs/records/Internacional_Expenses_Records.xlsx
@@ -1863,13 +1863,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13A3E564-97A2-42C4-888A-F0D27057907E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94510E3-3E78-4FDA-BD61-57609656BA0D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CC0FFF5-DF78-4BE4-94E0-35E54C438045}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C74F22F4-D8FB-40AD-AC95-F28D254CBE33}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED376326-09A4-4917-B5B8-58FACBFBC91E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{027DAE23-7E0A-4296-84D2-459BDF043A24}"/>
 </file>
--- a/ksoft_old/docs/records/Internacional_Expenses_Records.xlsx
+++ b/ksoft_old/docs/records/Internacional_Expenses_Records.xlsx
@@ -1863,13 +1863,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94510E3-3E78-4FDA-BD61-57609656BA0D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC150A9C-6EF2-4C54-83CD-C334BBB9272D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C74F22F4-D8FB-40AD-AC95-F28D254CBE33}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{378A24FA-E631-432F-B819-81E205D9A08C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{027DAE23-7E0A-4296-84D2-459BDF043A24}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371B6E86-4408-4A7D-9DFC-A9F752557E52}"/>
 </file>
--- a/ksoft_old/docs/records/Internacional_Expenses_Records.xlsx
+++ b/ksoft_old/docs/records/Internacional_Expenses_Records.xlsx
@@ -1863,13 +1863,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC150A9C-6EF2-4C54-83CD-C334BBB9272D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13A3E564-97A2-42C4-888A-F0D27057907E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{378A24FA-E631-432F-B819-81E205D9A08C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CC0FFF5-DF78-4BE4-94E0-35E54C438045}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371B6E86-4408-4A7D-9DFC-A9F752557E52}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED376326-09A4-4917-B5B8-58FACBFBC91E}"/>
 </file>